--- a/db/Data.xlsx
+++ b/db/Data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E2E544-B163-4F4E-AEC4-A5B58BE7444C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8A05EF-197F-4697-B946-FD9CC978F7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="3330" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3285" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4184" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4301" uniqueCount="1252">
   <si>
     <t>S01E01-13</t>
   </si>
@@ -3717,6 +3717,72 @@
   </si>
   <si>
     <t>The Copenhagen</t>
+  </si>
+  <si>
+    <t>Landman</t>
+  </si>
+  <si>
+    <t>Brave New World</t>
+  </si>
+  <si>
+    <t>Designated Survivor</t>
+  </si>
+  <si>
+    <t>Dune Prophecy</t>
+  </si>
+  <si>
+    <t>Fortitude</t>
+  </si>
+  <si>
+    <t>Into the Night</t>
+  </si>
+  <si>
+    <t>The OA</t>
+  </si>
+  <si>
+    <t>The Society</t>
+  </si>
+  <si>
+    <t>Bon Appetit Your Majesty</t>
+  </si>
+  <si>
+    <t>It is ok to not be ok</t>
+  </si>
+  <si>
+    <t>My love from the star</t>
+  </si>
+  <si>
+    <t>MyDearest</t>
+  </si>
+  <si>
+    <t>Youth of may</t>
+  </si>
+  <si>
+    <t>The Rain</t>
+  </si>
+  <si>
+    <t>The Stand</t>
+  </si>
+  <si>
+    <t>The Survivors</t>
+  </si>
+  <si>
+    <t>Y The Last Man</t>
+  </si>
+  <si>
+    <t>S08E01-11</t>
+  </si>
+  <si>
+    <t>Spartacus Gods of the Arena</t>
+  </si>
+  <si>
+    <t>Wolf Blood</t>
+  </si>
+  <si>
+    <t>Paradise</t>
+  </si>
+  <si>
+    <t>The Pitt</t>
   </si>
 </sst>
 </file>
@@ -4122,7 +4188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S828"/>
+  <dimension ref="A1:S852"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -7769,7 +7835,7 @@
         <v>489</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>396</v>
@@ -7782,6 +7848,9 @@
       </c>
       <c r="G195" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
@@ -9530,10 +9599,13 @@
         <v>551</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>962</v>
+      </c>
+      <c r="F285" s="1" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
@@ -9976,6 +10048,12 @@
       <c r="F306" s="1" t="s">
         <v>928</v>
       </c>
+      <c r="G306" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="H306" s="1" t="s">
+        <v>926</v>
+      </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
@@ -10158,6 +10236,9 @@
       <c r="F316" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="G316" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
@@ -11420,7 +11501,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>384</v>
       </c>
@@ -11434,7 +11515,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <v>385</v>
       </c>
@@ -11448,7 +11529,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
         <v>386</v>
       </c>
@@ -11468,7 +11549,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <v>387</v>
       </c>
@@ -11482,7 +11563,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <v>388</v>
       </c>
@@ -11499,7 +11580,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>389</v>
       </c>
@@ -11516,7 +11597,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <v>390</v>
       </c>
@@ -11530,7 +11611,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <v>391</v>
       </c>
@@ -11544,7 +11625,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <v>392</v>
       </c>
@@ -11567,7 +11648,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <v>393</v>
       </c>
@@ -11581,7 +11662,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
         <v>394</v>
       </c>
@@ -11601,7 +11682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <v>395</v>
       </c>
@@ -11621,7 +11702,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
         <v>396</v>
       </c>
@@ -11641,7 +11722,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
         <v>397</v>
       </c>
@@ -11664,7 +11745,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
         <v>398</v>
       </c>
@@ -11678,7 +11759,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <v>399</v>
       </c>
@@ -11686,7 +11767,7 @@
         <v>1026</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="D400" s="1" t="s">
         <v>396</v>
@@ -11711,6 +11792,9 @@
       </c>
       <c r="K400" s="1" t="s">
         <v>930</v>
+      </c>
+      <c r="L400" s="1" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
@@ -12235,7 +12319,7 @@
         <v>656</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>197</v>
@@ -12256,7 +12340,7 @@
         <v>924</v>
       </c>
       <c r="K430" s="1" t="s">
-        <v>922</v>
+        <v>278</v>
       </c>
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.25">
@@ -14116,6 +14200,9 @@
       <c r="H523" s="1" t="s">
         <v>942</v>
       </c>
+      <c r="I523" s="1" t="s">
+        <v>938</v>
+      </c>
     </row>
     <row r="524" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
@@ -14272,13 +14359,16 @@
         <v>722</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D530" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="F530" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.25">
@@ -15406,7 +15496,10 @@
         <v>927</v>
       </c>
       <c r="H584" s="1" t="s">
-        <v>17</v>
+        <v>926</v>
+      </c>
+      <c r="I584" s="1" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="585" spans="1:16" x14ac:dyDescent="0.25">
@@ -17355,10 +17448,13 @@
         <v>880</v>
       </c>
       <c r="C693" s="1" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="E693" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="F693" s="1" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="694" spans="1:15" x14ac:dyDescent="0.25">
@@ -18014,7 +18110,7 @@
         <v>754</v>
       </c>
       <c r="C727" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E727" s="1" t="s">
         <v>36</v>
@@ -18024,6 +18120,9 @@
       </c>
       <c r="G727" s="1" t="s">
         <v>927</v>
+      </c>
+      <c r="H727" s="1" t="s">
+        <v>943</v>
       </c>
     </row>
     <row r="728" spans="1:11" x14ac:dyDescent="0.25">
@@ -18896,6 +18995,9 @@
       <c r="E773" s="1" t="s">
         <v>959</v>
       </c>
+      <c r="F773" s="1" t="s">
+        <v>928</v>
+      </c>
     </row>
     <row r="774" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A774" s="1">
@@ -19493,6 +19595,9 @@
       <c r="F812" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="G812" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="813" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A813" s="1">
@@ -19703,10 +19808,442 @@
       <c r="A827" s="1">
         <v>826</v>
       </c>
+      <c r="B827" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C827" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E827" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F827" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="828" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A828" s="1">
         <v>827</v>
+      </c>
+      <c r="B828" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C828" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E828" s="1" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="829" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A829" s="1">
+        <v>828</v>
+      </c>
+      <c r="B829" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C829" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E829" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F829" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G829" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="830" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A830" s="1">
+        <v>829</v>
+      </c>
+      <c r="B830" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C830" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E830" s="1" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="831" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A831" s="1">
+        <v>830</v>
+      </c>
+      <c r="B831" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C831" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E831" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="832" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A832" s="1">
+        <v>831</v>
+      </c>
+      <c r="B832" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C832" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E832" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F832" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G832" s="1" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="833" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A833" s="1">
+        <v>832</v>
+      </c>
+      <c r="B833" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C833" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E833" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F833" s="1" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="834" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A834" s="1">
+        <v>833</v>
+      </c>
+      <c r="B834" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C834" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E834" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F834" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="G834" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="835" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A835" s="1">
+        <v>834</v>
+      </c>
+      <c r="B835" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C835" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E835" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="F835" s="1" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="836" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A836" s="1">
+        <v>835</v>
+      </c>
+      <c r="B836" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C836" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E836" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="837" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A837" s="1">
+        <v>836</v>
+      </c>
+      <c r="B837" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C837" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D837" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="E837" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="F837" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="G837" s="1" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="838" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A838" s="1">
+        <v>837</v>
+      </c>
+      <c r="B838" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C838" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D838" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="E838" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="839" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A839" s="1">
+        <v>838</v>
+      </c>
+      <c r="B839" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C839" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D839" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="E839" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="840" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A840" s="1">
+        <v>839</v>
+      </c>
+      <c r="B840" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C840" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D840" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="E840" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="841" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A841" s="1">
+        <v>840</v>
+      </c>
+      <c r="B841" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C841" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D841" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="E841" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="842" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A842" s="1">
+        <v>841</v>
+      </c>
+      <c r="B842" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C842" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D842" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="E842" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="843" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A843" s="1">
+        <v>842</v>
+      </c>
+      <c r="B843" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C843" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E843" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="F843" s="1" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="844" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A844" s="1">
+        <v>843</v>
+      </c>
+      <c r="B844" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C844" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E844" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="845" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A845" s="1">
+        <v>844</v>
+      </c>
+      <c r="B845" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C845" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E845" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="F845" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="G845" s="1" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="846" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A846" s="1">
+        <v>845</v>
+      </c>
+      <c r="B846" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C846" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E846" s="1" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="847" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A847" s="1">
+        <v>846</v>
+      </c>
+      <c r="B847" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C847" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E847" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="848" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A848" s="1">
+        <v>847</v>
+      </c>
+      <c r="B848" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C848" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E848" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A849" s="1">
+        <v>848</v>
+      </c>
+      <c r="B849" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C849" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E849" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A850" s="1">
+        <v>849</v>
+      </c>
+      <c r="B850" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C850" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E850" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F850" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G850" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H850" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I850" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A851" s="1">
+        <v>850</v>
+      </c>
+      <c r="B851" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C851" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E851" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="F851" s="1" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A852" s="1">
+        <v>851</v>
+      </c>
+      <c r="B852" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C852" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E852" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F852" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/db/Data.xlsx
+++ b/db/Data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3488883C-F7E8-4CE3-B476-AD963DFADA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF438348-29CF-4068-BA24-AA329112CB40}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{0B3BCB77-C46F-412C-A105-3F352329ABF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4105A4C-053E-4524-A182-14D6C3A0BDE6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4578" uniqueCount="1329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4609" uniqueCount="1327">
   <si>
     <t>S01E01-13</t>
   </si>
@@ -3769,21 +3769,12 @@
     <t>It's Okay to Not Be Okay</t>
   </si>
   <si>
-    <t>کره ای هست از فولدر سریز بیاد تو کره ای</t>
-  </si>
-  <si>
-    <t>Love Death and Robots</t>
-  </si>
-  <si>
     <t>not available in both tv maze and digi movies</t>
   </si>
   <si>
     <t>S01E01-60</t>
   </si>
   <si>
-    <t>از سریز بره تو انیمیشن</t>
-  </si>
-  <si>
     <t>Moon Knight</t>
   </si>
   <si>
@@ -4013,13 +4004,16 @@
   </si>
   <si>
     <t>S11E01-12</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4067,6 +4061,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4149,9 +4150,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4162,6 +4160,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4446,7 +4445,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:W885"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4494,7 +4492,7 @@
       <c r="R1" s="16"/>
       <c r="S1" s="16"/>
     </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4523,7 +4521,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4537,11 +4535,11 @@
         <v>901</v>
       </c>
     </row>
-    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>1244</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -4560,7 +4558,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4583,7 +4581,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -4606,7 +4604,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -4644,7 +4642,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -4658,7 +4656,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -4675,7 +4673,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -4689,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -4703,7 +4701,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -4717,7 +4715,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -4734,7 +4732,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4757,7 +4755,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4783,7 +4781,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -4797,7 +4795,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -4814,7 +4812,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -4828,7 +4826,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -4842,7 +4840,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -4856,7 +4854,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -4883,8 +4881,8 @@
       <c r="B22" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>370</v>
+      <c r="C22" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>901</v>
@@ -4900,8 +4898,8 @@
       <c r="B23" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>370</v>
+      <c r="C23" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>0</v>
@@ -4919,7 +4917,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -4933,7 +4931,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -4947,7 +4945,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -4964,7 +4962,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -4981,7 +4979,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -4995,7 +4993,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -5009,7 +5007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -5039,8 +5037,8 @@
       <c r="B31" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>370</v>
+      <c r="C31" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>931</v>
@@ -5061,7 +5059,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -5078,7 +5076,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -5092,7 +5090,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -5106,7 +5104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -5123,7 +5121,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -5137,7 +5135,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -5157,7 +5155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -5204,7 +5202,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -5218,7 +5216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -5259,8 +5257,8 @@
       <c r="B42" s="9" t="s">
         <v>1209</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>370</v>
+      <c r="C42" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>901</v>
@@ -5269,7 +5267,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -5283,7 +5281,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -5297,7 +5295,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -5317,7 +5315,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -5373,7 +5371,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -5390,7 +5388,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -5425,7 +5423,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -5445,7 +5443,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -5465,7 +5463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -5488,7 +5486,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -5505,7 +5503,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -5531,7 +5529,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -5554,7 +5552,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -5568,7 +5566,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -5589,8 +5587,8 @@
       <c r="B57" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>370</v>
+      <c r="C57" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>34</v>
@@ -5608,7 +5606,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -5656,7 +5654,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -5680,8 +5678,8 @@
       <c r="B62" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>370</v>
+      <c r="C62" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>34</v>
@@ -5694,8 +5692,8 @@
       <c r="B63" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>370</v>
+      <c r="C63" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>931</v>
@@ -5704,7 +5702,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -5718,7 +5716,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -5741,7 +5739,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -5758,7 +5756,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -5788,8 +5786,8 @@
       <c r="B68" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C68" s="10" t="s">
-        <v>370</v>
+      <c r="C68" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>60</v>
@@ -5801,7 +5799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -5834,8 +5832,8 @@
       <c r="B70" s="1" t="s">
         <v>1093</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>370</v>
+      <c r="C70" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>371</v>
@@ -5847,7 +5845,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -5861,7 +5859,7 @@
         <v>371</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>29</v>
@@ -5873,7 +5871,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -5903,8 +5901,8 @@
       <c r="B73" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>370</v>
+      <c r="C73" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>901</v>
@@ -5913,7 +5911,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -5936,7 +5934,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -5950,7 +5948,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -5974,8 +5972,8 @@
       <c r="B77" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C77" s="10" t="s">
-        <v>370</v>
+      <c r="C77" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>34</v>
@@ -5984,7 +5982,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -6001,7 +5999,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -6015,7 +6013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -6029,7 +6027,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -6049,7 +6047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -6078,7 +6076,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -6098,7 +6096,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -6150,7 +6148,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -6167,7 +6165,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -6187,7 +6185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -6201,7 +6199,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -6215,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -6247,7 +6245,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -6270,7 +6268,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -6287,7 +6285,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -6313,7 +6311,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -6327,7 +6325,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -6344,7 +6342,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -6391,8 +6389,8 @@
       <c r="B98" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C98" s="10" t="s">
-        <v>370</v>
+      <c r="C98" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>363</v>
@@ -6404,7 +6402,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -6428,8 +6426,8 @@
       <c r="B100" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>370</v>
+      <c r="C100" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>926</v>
@@ -6441,7 +6439,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -6461,7 +6459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -6482,8 +6480,8 @@
       <c r="B103" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>370</v>
+      <c r="C103" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>901</v>
@@ -6498,7 +6496,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -6524,7 +6522,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -6538,7 +6536,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -6579,8 +6577,8 @@
       <c r="B108" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>370</v>
+      <c r="C108" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>34</v>
@@ -6592,7 +6590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -6606,7 +6604,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -6637,7 +6635,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -6658,8 +6656,8 @@
       <c r="B113" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>370</v>
+      <c r="C113" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>901</v>
@@ -6674,7 +6672,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -6700,7 +6698,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -6717,7 +6715,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -6737,7 +6735,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -6772,7 +6770,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -6786,7 +6784,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -6800,7 +6798,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -6834,7 +6832,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -6851,7 +6849,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -6868,7 +6866,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -6885,7 +6883,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -6899,7 +6897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -6944,8 +6942,8 @@
       <c r="B127" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C127" s="10" t="s">
-        <v>370</v>
+      <c r="C127" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>371</v>
@@ -6957,7 +6955,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -6974,7 +6972,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -6988,7 +6986,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -7006,13 +7004,13 @@
       <c r="A131" s="1">
         <v>130</v>
       </c>
-      <c r="B131" s="15" t="s">
+      <c r="B131" s="14" t="s">
         <v>350</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="D131" s="15"/>
+      <c r="D131" s="14"/>
       <c r="E131" s="1" t="s">
         <v>5</v>
       </c>
@@ -7047,13 +7045,13 @@
         <v>883</v>
       </c>
       <c r="P131" s="1" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="Q131" s="1" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
@@ -7095,8 +7093,8 @@
       <c r="B133" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="C133" s="10" t="s">
-        <v>370</v>
+      <c r="C133" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>363</v>
@@ -7105,7 +7103,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -7131,7 +7129,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -7158,8 +7156,8 @@
       <c r="B136" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="C136" s="10" t="s">
-        <v>370</v>
+      <c r="C136" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>363</v>
@@ -7175,8 +7173,8 @@
       <c r="B137" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C137" s="10" t="s">
-        <v>370</v>
+      <c r="C137" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>926</v>
@@ -7216,7 +7214,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -7230,7 +7228,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -7247,7 +7245,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -7261,7 +7259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -7295,7 +7293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -7312,7 +7310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -7326,7 +7324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -7340,7 +7338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -7354,7 +7352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -7395,8 +7393,8 @@
       <c r="B151" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C151" s="10" t="s">
-        <v>370</v>
+      <c r="C151" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>901</v>
@@ -7405,7 +7403,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -7436,7 +7434,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -7450,7 +7448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -7464,7 +7462,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -7484,7 +7482,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -7518,7 +7516,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -7532,7 +7530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -7546,7 +7544,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -7573,8 +7571,8 @@
       <c r="B162" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C162" s="10" t="s">
-        <v>370</v>
+      <c r="C162" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>34</v>
@@ -7586,7 +7584,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -7600,7 +7598,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -7620,7 +7618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -7640,7 +7638,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -7678,8 +7676,8 @@
       <c r="B168" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C168" s="10" t="s">
-        <v>370</v>
+      <c r="C168" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>926</v>
@@ -7694,7 +7692,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -7708,7 +7706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -7725,7 +7723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -7739,7 +7737,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -7753,7 +7751,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -7774,14 +7772,14 @@
       <c r="B174" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C174" s="10" t="s">
-        <v>370</v>
+      <c r="C174" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -7798,7 +7796,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -7863,7 +7861,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -7889,7 +7887,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -7906,7 +7904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -7941,7 +7939,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -7955,7 +7953,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -7990,7 +7988,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -8004,7 +8002,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -8018,7 +8016,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -8042,14 +8040,14 @@
       <c r="B188" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="C188" s="10" t="s">
-        <v>370</v>
+      <c r="C188" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -8066,7 +8064,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -8119,7 +8117,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -8139,7 +8137,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -8156,7 +8154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -8179,7 +8177,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -8203,8 +8201,8 @@
       <c r="B195" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C195" s="10" t="s">
-        <v>370</v>
+      <c r="C195" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>383</v>
@@ -8219,10 +8217,10 @@
         <v>27</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -8250,7 +8248,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -8264,7 +8262,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -8278,7 +8276,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -8310,7 +8308,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -8349,8 +8347,8 @@
       <c r="B202" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C202" s="10" t="s">
-        <v>370</v>
+      <c r="C202" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>901</v>
@@ -8384,8 +8382,8 @@
       <c r="B203" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="C203" s="10" t="s">
-        <v>370</v>
+      <c r="C203" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>34</v>
@@ -8417,7 +8415,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>204</v>
       </c>
@@ -8455,7 +8453,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>205</v>
       </c>
@@ -8495,7 +8493,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -8516,8 +8514,8 @@
       <c r="B209" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C209" s="10" t="s">
-        <v>370</v>
+      <c r="C209" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>901</v>
@@ -8526,7 +8524,7 @@
         <v>900</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
@@ -8552,7 +8550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>210</v>
       </c>
@@ -8566,7 +8564,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>211</v>
       </c>
@@ -8583,7 +8581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>212</v>
       </c>
@@ -8614,7 +8612,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>214</v>
       </c>
@@ -8628,7 +8626,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>215</v>
       </c>
@@ -8661,8 +8659,8 @@
       <c r="B217" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="C217" s="10" t="s">
-        <v>370</v>
+      <c r="C217" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>936</v>
@@ -8671,7 +8669,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>217</v>
       </c>
@@ -8685,7 +8683,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>218</v>
       </c>
@@ -8711,7 +8709,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>219</v>
       </c>
@@ -8725,7 +8723,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>220</v>
       </c>
@@ -8742,7 +8740,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>221</v>
       </c>
@@ -8777,7 +8775,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>222</v>
       </c>
@@ -8794,7 +8792,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>223</v>
       </c>
@@ -8808,7 +8806,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>224</v>
       </c>
@@ -8874,7 +8872,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>227</v>
       </c>
@@ -8888,7 +8886,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>228</v>
       </c>
@@ -8905,7 +8903,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>229</v>
       </c>
@@ -8945,7 +8943,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>231</v>
       </c>
@@ -8966,8 +8964,8 @@
       <c r="B233" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C233" s="10" t="s">
-        <v>370</v>
+      <c r="C233" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>34</v>
@@ -8986,14 +8984,14 @@
       <c r="B234" s="1" t="s">
         <v>969</v>
       </c>
-      <c r="C234" s="10" t="s">
-        <v>370</v>
+      <c r="C234" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>234</v>
       </c>
@@ -9007,7 +9005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>235</v>
       </c>
@@ -9048,7 +9046,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>236</v>
       </c>
@@ -9081,8 +9079,8 @@
       <c r="B238" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C238" s="10" t="s">
-        <v>370</v>
+      <c r="C238" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>34</v>
@@ -9097,7 +9095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>238</v>
       </c>
@@ -9114,7 +9112,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>239</v>
       </c>
@@ -9186,7 +9184,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>242</v>
       </c>
@@ -9221,7 +9219,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>243</v>
       </c>
@@ -9259,8 +9257,8 @@
       <c r="B246" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="C246" s="10" t="s">
-        <v>370</v>
+      <c r="C246" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>930</v>
@@ -9272,7 +9270,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>246</v>
       </c>
@@ -9289,7 +9287,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>247</v>
       </c>
@@ -9341,7 +9339,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>249</v>
       </c>
@@ -9396,8 +9394,8 @@
       <c r="B253" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C253" s="10" t="s">
-        <v>370</v>
+      <c r="C253" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>34</v>
@@ -9406,7 +9404,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="254" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>253</v>
       </c>
@@ -9432,7 +9430,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>254</v>
       </c>
@@ -9446,7 +9444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>255</v>
       </c>
@@ -9460,7 +9458,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="257" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>256</v>
       </c>
@@ -9489,7 +9487,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>257</v>
       </c>
@@ -9503,7 +9501,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>258</v>
       </c>
@@ -9517,7 +9515,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>259</v>
       </c>
@@ -9531,7 +9529,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>260</v>
       </c>
@@ -9558,8 +9556,8 @@
       <c r="B262" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="C262" s="10" t="s">
-        <v>370</v>
+      <c r="C262" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>34</v>
@@ -9577,7 +9575,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>262</v>
       </c>
@@ -9594,7 +9592,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="264" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>263</v>
       </c>
@@ -9608,7 +9606,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>264</v>
       </c>
@@ -9631,7 +9629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>265</v>
       </c>
@@ -9651,7 +9649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="267" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>266</v>
       </c>
@@ -9665,7 +9663,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="268" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>267</v>
       </c>
@@ -9679,7 +9677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>268</v>
       </c>
@@ -9743,7 +9741,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="271" spans="1:14" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>270</v>
       </c>
@@ -9764,8 +9762,8 @@
       <c r="B272" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="C272" s="10" t="s">
-        <v>370</v>
+      <c r="C272" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>371</v>
@@ -9777,7 +9775,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>272</v>
       </c>
@@ -9794,7 +9792,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>273</v>
       </c>
@@ -9811,7 +9809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>274</v>
       </c>
@@ -9837,7 +9835,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>275</v>
       </c>
@@ -9864,14 +9862,14 @@
       <c r="B277" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C277" s="10" t="s">
-        <v>370</v>
+      <c r="C277" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>277</v>
       </c>
@@ -9911,7 +9909,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>279</v>
       </c>
@@ -9934,7 +9932,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>280</v>
       </c>
@@ -9948,7 +9946,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="282" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>281</v>
       </c>
@@ -9972,8 +9970,8 @@
       <c r="B283" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="C283" s="10" t="s">
-        <v>370</v>
+      <c r="C283" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>901</v>
@@ -9985,7 +9983,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>283</v>
       </c>
@@ -10002,7 +10000,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>284</v>
       </c>
@@ -10022,7 +10020,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>285</v>
       </c>
@@ -10057,7 +10055,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>286</v>
       </c>
@@ -10081,8 +10079,8 @@
       <c r="B288" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="C288" s="10" t="s">
-        <v>370</v>
+      <c r="C288" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>901</v>
@@ -10123,7 +10121,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>289</v>
       </c>
@@ -10159,8 +10157,8 @@
       <c r="B291" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C291" s="10" t="s">
-        <v>370</v>
+      <c r="C291" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>34</v>
@@ -10169,10 +10167,10 @@
         <v>900</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="292" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>291</v>
       </c>
@@ -10210,7 +10208,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>292</v>
       </c>
@@ -10224,7 +10222,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>293</v>
       </c>
@@ -10241,7 +10239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>294</v>
       </c>
@@ -10261,7 +10259,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="296" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>295</v>
       </c>
@@ -10278,7 +10276,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>296</v>
       </c>
@@ -10298,7 +10296,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="298" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>297</v>
       </c>
@@ -10319,8 +10317,8 @@
       <c r="B299" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="C299" s="10" t="s">
-        <v>370</v>
+      <c r="C299" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>901</v>
@@ -10364,7 +10362,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="301" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>300</v>
       </c>
@@ -10385,8 +10383,8 @@
       <c r="B302" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="C302" s="10" t="s">
-        <v>370</v>
+      <c r="C302" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>931</v>
@@ -10398,7 +10396,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="303" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>302</v>
       </c>
@@ -10412,7 +10410,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="304" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>303</v>
       </c>
@@ -10432,7 +10430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>304</v>
       </c>
@@ -10458,7 +10456,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>305</v>
       </c>
@@ -10475,7 +10473,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>306</v>
       </c>
@@ -10503,7 +10501,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>308</v>
       </c>
@@ -10526,7 +10524,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>309</v>
       </c>
@@ -10543,7 +10541,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>310</v>
       </c>
@@ -10569,7 +10567,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>311</v>
       </c>
@@ -10589,7 +10587,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>312</v>
       </c>
@@ -10603,7 +10601,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>313</v>
       </c>
@@ -10620,7 +10618,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>314</v>
       </c>
@@ -10643,7 +10641,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>315</v>
       </c>
@@ -10671,7 +10669,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>317</v>
       </c>
@@ -10699,13 +10697,13 @@
         <v>383</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>319</v>
       </c>
@@ -10719,7 +10717,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>320</v>
       </c>
@@ -10743,8 +10741,8 @@
       <c r="B322" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C322" s="10" t="s">
-        <v>370</v>
+      <c r="C322" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>363</v>
@@ -10753,7 +10751,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>322</v>
       </c>
@@ -10776,7 +10774,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>323</v>
       </c>
@@ -10803,8 +10801,8 @@
       <c r="B325" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C325" s="10" t="s">
-        <v>370</v>
+      <c r="C325" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>34</v>
@@ -10823,14 +10821,14 @@
       <c r="B326" s="1" t="s">
         <v>1029</v>
       </c>
-      <c r="C326" s="10" t="s">
-        <v>370</v>
+      <c r="C326" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>326</v>
       </c>
@@ -10856,7 +10854,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="328" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>327</v>
       </c>
@@ -10870,7 +10868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>328</v>
       </c>
@@ -10884,7 +10882,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="330" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>329</v>
       </c>
@@ -10914,14 +10912,14 @@
       <c r="B331" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C331" s="10" t="s">
-        <v>370</v>
+      <c r="C331" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>331</v>
       </c>
@@ -10938,7 +10936,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>332</v>
       </c>
@@ -10987,7 +10985,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>334</v>
       </c>
@@ -11001,7 +10999,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>335</v>
       </c>
@@ -11015,7 +11013,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="337" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>336</v>
       </c>
@@ -11041,7 +11039,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="338" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>337</v>
       </c>
@@ -11055,7 +11053,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="339" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>338</v>
       </c>
@@ -11089,7 +11087,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="341" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>340</v>
       </c>
@@ -11113,8 +11111,8 @@
       <c r="B342" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="C342" s="10" t="s">
-        <v>370</v>
+      <c r="C342" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>363</v>
@@ -11123,7 +11121,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="343" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>342</v>
       </c>
@@ -11143,7 +11141,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="344" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>343</v>
       </c>
@@ -11157,7 +11155,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="345" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>344</v>
       </c>
@@ -11180,7 +11178,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="346" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>345</v>
       </c>
@@ -11197,7 +11195,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="347" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>346</v>
       </c>
@@ -11226,7 +11224,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="348" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>347</v>
       </c>
@@ -11252,7 +11250,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="349" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>348</v>
       </c>
@@ -11279,8 +11277,8 @@
       <c r="B350" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="C350" s="10" t="s">
-        <v>370</v>
+      <c r="C350" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>363</v>
@@ -11296,8 +11294,8 @@
       <c r="B351" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="C351" s="10" t="s">
-        <v>370</v>
+      <c r="C351" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>371</v>
@@ -11315,7 +11313,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="352" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>351</v>
       </c>
@@ -11339,8 +11337,8 @@
       <c r="B353" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="C353" s="10" t="s">
-        <v>370</v>
+      <c r="C353" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>363</v>
@@ -11349,7 +11347,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>353</v>
       </c>
@@ -11363,7 +11361,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>354</v>
       </c>
@@ -11392,7 +11390,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>355</v>
       </c>
@@ -11429,7 +11427,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>357</v>
       </c>
@@ -11458,7 +11456,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>358</v>
       </c>
@@ -11475,7 +11473,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>359</v>
       </c>
@@ -11506,7 +11504,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>361</v>
       </c>
@@ -11529,7 +11527,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -11543,7 +11541,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>363</v>
       </c>
@@ -11560,7 +11558,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>364</v>
       </c>
@@ -11598,8 +11596,8 @@
       <c r="B367" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="C367" s="10" t="s">
-        <v>370</v>
+      <c r="C367" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>926</v>
@@ -11608,7 +11606,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>367</v>
       </c>
@@ -11622,7 +11620,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>368</v>
       </c>
@@ -11648,7 +11646,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="370" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>369</v>
       </c>
@@ -11678,8 +11676,8 @@
       <c r="B371" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="C371" s="10" t="s">
-        <v>370</v>
+      <c r="C371" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>901</v>
@@ -11691,7 +11689,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="372" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>371</v>
       </c>
@@ -11723,7 +11721,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="373" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>372</v>
       </c>
@@ -11749,7 +11747,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="374" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>373</v>
       </c>
@@ -11763,7 +11761,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="375" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>374</v>
       </c>
@@ -11780,7 +11778,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="376" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>375</v>
       </c>
@@ -11804,8 +11802,8 @@
       <c r="B377" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="C377" s="10" t="s">
-        <v>370</v>
+      <c r="C377" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>363</v>
@@ -11821,8 +11819,8 @@
       <c r="B378" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="C378" s="10" t="s">
-        <v>370</v>
+      <c r="C378" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D378" s="1" t="s">
         <v>363</v>
@@ -11855,8 +11853,8 @@
       <c r="B380" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="C380" s="10" t="s">
-        <v>370</v>
+      <c r="C380" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>5</v>
@@ -11889,7 +11887,7 @@
         <v>774</v>
       </c>
       <c r="O380" s="1" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="381" spans="1:15" x14ac:dyDescent="0.25">
@@ -11899,8 +11897,8 @@
       <c r="B381" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="C381" s="10" t="s">
-        <v>370</v>
+      <c r="C381" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>34</v>
@@ -11909,7 +11907,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="382" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>381</v>
       </c>
@@ -11935,7 +11933,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="383" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>382</v>
       </c>
@@ -11952,7 +11950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="384" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>383</v>
       </c>
@@ -11966,7 +11964,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="385" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>384</v>
       </c>
@@ -11980,7 +11978,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="386" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <v>385</v>
       </c>
@@ -12005,16 +12003,16 @@
         <v>386</v>
       </c>
       <c r="B387" s="9" t="s">
-        <v>1252</v>
-      </c>
-      <c r="C387" s="10" t="s">
-        <v>370</v>
+        <v>1249</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="388" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <v>387</v>
       </c>
@@ -12031,7 +12029,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="389" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <v>388</v>
       </c>
@@ -12048,7 +12046,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="390" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>389</v>
       </c>
@@ -12062,7 +12060,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="391" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <v>390</v>
       </c>
@@ -12076,7 +12074,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="392" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <v>391</v>
       </c>
@@ -12099,7 +12097,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="393" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <v>392</v>
       </c>
@@ -12113,7 +12111,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="394" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <v>393</v>
       </c>
@@ -12173,7 +12171,7 @@
         <v>34</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>920</v>
@@ -12186,8 +12184,8 @@
       <c r="B397" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="C397" s="10" t="s">
-        <v>370</v>
+      <c r="C397" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>901</v>
@@ -12226,8 +12224,8 @@
       <c r="B399" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="C399" s="10" t="s">
-        <v>370</v>
+      <c r="C399" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>383</v>
@@ -12251,13 +12249,13 @@
         <v>165</v>
       </c>
       <c r="K399" s="1" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="L399" s="1" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="400" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <v>399</v>
       </c>
@@ -12274,7 +12272,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>400</v>
       </c>
@@ -12298,8 +12296,8 @@
       <c r="B402" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="C402" s="10" t="s">
-        <v>370</v>
+      <c r="C402" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D402" s="1" t="s">
         <v>363</v>
@@ -12346,8 +12344,8 @@
       <c r="B405" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="C405" s="10" t="s">
-        <v>370</v>
+      <c r="C405" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>901</v>
@@ -12363,8 +12361,8 @@
       <c r="B406" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="C406" s="10" t="s">
-        <v>370</v>
+      <c r="C406" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>5</v>
@@ -12395,8 +12393,8 @@
       <c r="B407" s="9" t="s">
         <v>1230</v>
       </c>
-      <c r="C407" s="10" t="s">
-        <v>370</v>
+      <c r="C407" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>22</v>
@@ -12405,7 +12403,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
         <v>407</v>
       </c>
@@ -12435,8 +12433,8 @@
       <c r="B409" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="C409" s="10" t="s">
-        <v>370</v>
+      <c r="C409" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="D409" s="1" t="s">
         <v>383</v>
@@ -12452,8 +12450,8 @@
       <c r="B410" s="1" t="s">
         <v>1099</v>
       </c>
-      <c r="C410" s="10" t="s">
-        <v>370</v>
+      <c r="C410" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D410" s="1" t="s">
         <v>363</v>
@@ -12462,7 +12460,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="411" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
         <v>410</v>
       </c>
@@ -12476,7 +12474,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
         <v>411</v>
       </c>
@@ -12504,7 +12502,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="414" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
         <v>413</v>
       </c>
@@ -12532,7 +12530,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
         <v>415</v>
       </c>
@@ -12571,8 +12569,8 @@
       <c r="B417" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C417" s="10" t="s">
-        <v>370</v>
+      <c r="C417" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>338</v>
@@ -12595,7 +12593,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="419" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
         <v>418</v>
       </c>
@@ -12616,8 +12614,8 @@
       <c r="B420" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C420" s="10" t="s">
-        <v>370</v>
+      <c r="C420" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>34</v>
@@ -12635,7 +12633,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="421" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
         <v>420</v>
       </c>
@@ -12667,7 +12665,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="422" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
         <v>421</v>
       </c>
@@ -12700,8 +12698,8 @@
       <c r="B423" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="C423" s="10" t="s">
-        <v>370</v>
+      <c r="C423" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="D423" s="1" t="s">
         <v>383</v>
@@ -12716,7 +12714,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="424" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
         <v>423</v>
       </c>
@@ -12730,7 +12728,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="425" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
         <v>424</v>
       </c>
@@ -12770,7 +12768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="427" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
         <v>426</v>
       </c>
@@ -12794,8 +12792,8 @@
       <c r="B428" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="C428" s="10" t="s">
-        <v>370</v>
+      <c r="C428" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>191</v>
@@ -12822,7 +12820,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="429" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
         <v>428</v>
       </c>
@@ -12836,7 +12834,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="430" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
         <v>429</v>
       </c>
@@ -12872,8 +12870,8 @@
       <c r="B431" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C431" s="10" t="s">
-        <v>370</v>
+      <c r="C431" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>34</v>
@@ -12895,8 +12893,8 @@
       <c r="B432" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="C432" s="10" t="s">
-        <v>370</v>
+      <c r="C432" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="D432" s="1" t="s">
         <v>363</v>
@@ -12932,8 +12930,8 @@
       <c r="B434" s="1" t="s">
         <v>992</v>
       </c>
-      <c r="C434" s="10" t="s">
-        <v>370</v>
+      <c r="C434" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>34</v>
@@ -12956,7 +12954,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
         <v>435</v>
       </c>
@@ -12976,7 +12974,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="437" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
         <v>436</v>
       </c>
@@ -12993,7 +12991,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
         <v>437</v>
       </c>
@@ -13025,7 +13023,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
         <v>438</v>
       </c>
@@ -13042,7 +13040,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
         <v>439</v>
       </c>
@@ -13078,7 +13076,7 @@
       <c r="B441" s="9" t="s">
         <v>1232</v>
       </c>
-      <c r="C441" s="5" t="s">
+      <c r="C441" s="10" t="s">
         <v>370</v>
       </c>
       <c r="D441" s="1" t="s">
@@ -13088,7 +13086,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
         <v>441</v>
       </c>
@@ -13108,7 +13106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
         <v>442</v>
       </c>
@@ -13128,7 +13126,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
         <v>443</v>
       </c>
@@ -13165,7 +13163,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
         <v>445</v>
       </c>
@@ -13189,8 +13187,8 @@
       <c r="B447" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="C447" s="10" t="s">
-        <v>370</v>
+      <c r="C447" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>901</v>
@@ -13199,7 +13197,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
         <v>447</v>
       </c>
@@ -13225,7 +13223,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
         <v>448</v>
       </c>
@@ -13239,7 +13237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
         <v>449</v>
       </c>
@@ -13259,7 +13257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
         <v>450</v>
       </c>
@@ -13276,7 +13274,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
         <v>451</v>
       </c>
@@ -13299,7 +13297,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
         <v>452</v>
       </c>
@@ -13316,7 +13314,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
         <v>453</v>
       </c>
@@ -13333,7 +13331,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="455" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
         <v>454</v>
       </c>
@@ -13359,7 +13357,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="456" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
         <v>455</v>
       </c>
@@ -13395,8 +13393,8 @@
       <c r="B457" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="C457" s="10" t="s">
-        <v>370</v>
+      <c r="C457" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>34</v>
@@ -13418,8 +13416,8 @@
       <c r="B458" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C458" s="10" t="s">
-        <v>370</v>
+      <c r="C458" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>34</v>
@@ -13431,7 +13429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
         <v>458</v>
       </c>
@@ -13471,7 +13469,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
         <v>460</v>
       </c>
@@ -13485,7 +13483,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
         <v>461</v>
       </c>
@@ -13524,8 +13522,8 @@
       <c r="B463" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="C463" s="10" t="s">
-        <v>370</v>
+      <c r="C463" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>34</v>
@@ -13534,7 +13532,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
         <v>463</v>
       </c>
@@ -13560,7 +13558,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="465" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
         <v>464</v>
       </c>
@@ -13574,7 +13572,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="466" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
         <v>465</v>
       </c>
@@ -13612,7 +13610,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="467" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
         <v>466</v>
       </c>
@@ -13629,7 +13627,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="468" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
         <v>467</v>
       </c>
@@ -13660,7 +13658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
         <v>469</v>
       </c>
@@ -13677,7 +13675,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="471" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
         <v>470</v>
       </c>
@@ -13709,7 +13707,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="472" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
         <v>471</v>
       </c>
@@ -13729,7 +13727,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="473" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
         <v>472</v>
       </c>
@@ -13743,7 +13741,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="474" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
         <v>473</v>
       </c>
@@ -13758,7 +13756,7 @@
       </c>
       <c r="K474" s="3"/>
     </row>
-    <row r="475" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
         <v>474</v>
       </c>
@@ -13781,7 +13779,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="476" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
         <v>475</v>
       </c>
@@ -13798,7 +13796,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="477" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
         <v>476</v>
       </c>
@@ -13819,8 +13817,8 @@
       <c r="B478" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C478" s="10" t="s">
-        <v>370</v>
+      <c r="C478" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>901</v>
@@ -13833,8 +13831,8 @@
       <c r="B479" s="9" t="s">
         <v>1234</v>
       </c>
-      <c r="C479" s="10" t="s">
-        <v>370</v>
+      <c r="C479" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>34</v>
@@ -13849,7 +13847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="480" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
         <v>479</v>
       </c>
@@ -13866,7 +13864,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="481" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
         <v>480</v>
       </c>
@@ -13927,7 +13925,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="483" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
         <v>482</v>
       </c>
@@ -13946,10 +13944,10 @@
         <v>483</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C484" s="10" t="s">
-        <v>370</v>
+        <v>1322</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>901</v>
@@ -13958,7 +13956,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="485" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
         <v>484</v>
       </c>
@@ -14013,7 +14011,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="487" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
         <v>486</v>
       </c>
@@ -14030,7 +14028,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="488" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
         <v>487</v>
       </c>
@@ -14052,13 +14050,13 @@
         <v>488</v>
       </c>
       <c r="B489" s="9" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C489" s="10" t="s">
-        <v>370</v>
+        <v>1321</v>
+      </c>
+      <c r="C489" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>22</v>
@@ -14067,7 +14065,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="490" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
         <v>489</v>
       </c>
@@ -14087,7 +14085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
         <v>490</v>
       </c>
@@ -14104,7 +14102,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="492" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
         <v>491</v>
       </c>
@@ -14125,8 +14123,8 @@
       <c r="B493" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="C493" s="10" t="s">
-        <v>370</v>
+      <c r="C493" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D493" s="1" t="s">
         <v>371</v>
@@ -14138,7 +14136,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="494" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
         <v>493</v>
       </c>
@@ -14164,7 +14162,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="495" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
         <v>494</v>
       </c>
@@ -14178,7 +14176,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="496" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
         <v>495</v>
       </c>
@@ -14202,8 +14200,8 @@
       <c r="B497" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C497" s="10" t="s">
-        <v>370</v>
+      <c r="C497" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>67</v>
@@ -14225,8 +14223,8 @@
       <c r="B498" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="C498" s="10" t="s">
-        <v>370</v>
+      <c r="C498" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>5</v>
@@ -14256,7 +14254,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
         <v>498</v>
       </c>
@@ -14288,7 +14286,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
         <v>499</v>
       </c>
@@ -14302,7 +14300,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
         <v>500</v>
       </c>
@@ -14322,7 +14320,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="502" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
         <v>501</v>
       </c>
@@ -14346,8 +14344,8 @@
       <c r="B503" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C503" s="10" t="s">
-        <v>370</v>
+      <c r="C503" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>34</v>
@@ -14362,7 +14360,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
         <v>503</v>
       </c>
@@ -14376,7 +14374,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="505" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
         <v>504</v>
       </c>
@@ -14417,8 +14415,8 @@
       <c r="B507" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="C507" s="10" t="s">
-        <v>370</v>
+      <c r="C507" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>901</v>
@@ -14427,7 +14425,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="508" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
         <v>507</v>
       </c>
@@ -14452,7 +14450,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="9" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="C509" s="10" t="s">
         <v>370</v>
@@ -14482,16 +14480,16 @@
         <v>131</v>
       </c>
       <c r="M509" s="1" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="N509" s="1" t="s">
         <v>875</v>
       </c>
       <c r="O509" s="1" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="510" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
         <v>509</v>
       </c>
@@ -14505,7 +14503,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="511" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
         <v>510</v>
       </c>
@@ -14528,7 +14526,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="512" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
         <v>511</v>
       </c>
@@ -14560,7 +14558,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="513" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
         <v>512</v>
       </c>
@@ -14577,7 +14575,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="514" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
         <v>513</v>
       </c>
@@ -14598,8 +14596,8 @@
       <c r="B515" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C515" s="10" t="s">
-        <v>370</v>
+      <c r="C515" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>34</v>
@@ -14625,7 +14623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
         <v>516</v>
       </c>
@@ -14671,10 +14669,10 @@
         <v>29</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="519" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="519" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
         <v>518</v>
       </c>
@@ -14700,7 +14698,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="520" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
         <v>519</v>
       </c>
@@ -14749,7 +14747,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="522" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
         <v>521</v>
       </c>
@@ -14790,7 +14788,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="523" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
         <v>522</v>
       </c>
@@ -14807,7 +14805,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="524" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
         <v>523</v>
       </c>
@@ -14844,7 +14842,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="526" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
         <v>525</v>
       </c>
@@ -14899,7 +14897,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="528" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
         <v>527</v>
       </c>
@@ -14919,7 +14917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
         <v>528</v>
       </c>
@@ -14940,8 +14938,8 @@
       <c r="B530" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="C530" s="10" t="s">
-        <v>370</v>
+      <c r="C530" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D530" s="1" t="s">
         <v>371</v>
@@ -14956,7 +14954,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
         <v>530</v>
       </c>
@@ -14988,7 +14986,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
         <v>531</v>
       </c>
@@ -15005,7 +15003,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
         <v>532</v>
       </c>
@@ -15056,7 +15054,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
         <v>535</v>
       </c>
@@ -15096,7 +15094,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="538" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
         <v>537</v>
       </c>
@@ -15110,7 +15108,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="539" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
         <v>538</v>
       </c>
@@ -15124,7 +15122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
         <v>539</v>
       </c>
@@ -15151,8 +15149,8 @@
       <c r="B541" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="C541" s="10" t="s">
-        <v>370</v>
+      <c r="C541" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>34</v>
@@ -15164,7 +15162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="542" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
         <v>541</v>
       </c>
@@ -15184,7 +15182,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
         <v>542</v>
       </c>
@@ -15210,7 +15208,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A544" s="1">
         <v>543</v>
       </c>
@@ -15230,7 +15228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="545" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
         <v>544</v>
       </c>
@@ -15256,7 +15254,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="546" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A546" s="1">
         <v>545</v>
       </c>
@@ -15291,7 +15289,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="547" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A547" s="1">
         <v>546</v>
       </c>
@@ -15321,8 +15319,8 @@
       <c r="B548" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="C548" s="10" t="s">
-        <v>370</v>
+      <c r="C548" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>901</v>
@@ -15348,7 +15346,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A550" s="1">
         <v>549</v>
       </c>
@@ -15386,7 +15384,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
         <v>550</v>
       </c>
@@ -15415,7 +15413,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A552" s="1">
         <v>551</v>
       </c>
@@ -15438,7 +15436,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
         <v>552</v>
       </c>
@@ -15494,7 +15492,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
         <v>553</v>
       </c>
@@ -15508,7 +15506,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
         <v>554</v>
       </c>
@@ -15528,7 +15526,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="556" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
         <v>555</v>
       </c>
@@ -15548,7 +15546,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A557" s="1">
         <v>556</v>
       </c>
@@ -15569,8 +15567,8 @@
       <c r="B558" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="C558" s="10" t="s">
-        <v>370</v>
+      <c r="C558" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>22</v>
@@ -15586,14 +15584,14 @@
       <c r="B559" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="C559" s="10" t="s">
-        <v>370</v>
+      <c r="C559" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
         <v>559</v>
       </c>
@@ -15614,8 +15612,8 @@
       <c r="B561" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="C561" s="10" t="s">
-        <v>370</v>
+      <c r="C561" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>931</v>
@@ -15624,7 +15622,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="562" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
         <v>561</v>
       </c>
@@ -15653,7 +15651,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="563" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
         <v>562</v>
       </c>
@@ -15670,7 +15668,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="564" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
         <v>563</v>
       </c>
@@ -15687,7 +15685,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="565" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
         <v>564</v>
       </c>
@@ -15701,7 +15699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
         <v>565</v>
       </c>
@@ -15715,7 +15713,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="567" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
         <v>566</v>
       </c>
@@ -15747,7 +15745,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="568" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
         <v>567</v>
       </c>
@@ -15761,7 +15759,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="569" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
         <v>568</v>
       </c>
@@ -15814,8 +15812,8 @@
       <c r="B571" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="C571" s="10" t="s">
-        <v>370</v>
+      <c r="C571" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>901</v>
@@ -15824,7 +15822,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="572" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
         <v>571</v>
       </c>
@@ -15848,8 +15846,8 @@
       <c r="B573" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="C573" s="10" t="s">
-        <v>370</v>
+      <c r="C573" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D573" s="1" t="s">
         <v>363</v>
@@ -15865,8 +15863,8 @@
       <c r="B574" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="C574" s="10" t="s">
-        <v>370</v>
+      <c r="C574" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>901</v>
@@ -15884,7 +15882,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="575" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
         <v>574</v>
       </c>
@@ -15901,7 +15899,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="576" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A576" s="1">
         <v>575</v>
       </c>
@@ -15915,7 +15913,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A577" s="1">
         <v>576</v>
       </c>
@@ -15929,7 +15927,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A578" s="1">
         <v>577</v>
       </c>
@@ -15983,8 +15981,8 @@
       <c r="B579" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="C579" s="10" t="s">
-        <v>370</v>
+      <c r="C579" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>34</v>
@@ -15993,7 +15991,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A580" s="1">
         <v>579</v>
       </c>
@@ -16034,7 +16032,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A581" s="1">
         <v>580</v>
       </c>
@@ -16054,7 +16052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A582" s="1">
         <v>581</v>
       </c>
@@ -16080,7 +16078,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A583" s="1">
         <v>582</v>
       </c>
@@ -16097,7 +16095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A584" s="1">
         <v>583</v>
       </c>
@@ -16118,8 +16116,8 @@
       <c r="B585" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="C585" s="10" t="s">
-        <v>370</v>
+      <c r="C585" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>901</v>
@@ -16128,7 +16126,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A586" s="1">
         <v>585</v>
       </c>
@@ -16154,7 +16152,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A587" s="1">
         <v>586</v>
       </c>
@@ -16175,8 +16173,8 @@
       <c r="B588" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="C588" s="10" t="s">
-        <v>370</v>
+      <c r="C588" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>926</v>
@@ -16211,7 +16209,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A590" s="1">
         <v>589</v>
       </c>
@@ -16232,8 +16230,8 @@
       <c r="B591" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="C591" s="10" t="s">
-        <v>370</v>
+      <c r="C591" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>34</v>
@@ -16255,8 +16253,8 @@
       <c r="B592" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="C592" s="10" t="s">
-        <v>370</v>
+      <c r="C592" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>934</v>
@@ -16276,7 +16274,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="594" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A594" s="1">
         <v>593</v>
       </c>
@@ -16290,7 +16288,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="595" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A595" s="1">
         <v>594</v>
       </c>
@@ -16304,7 +16302,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="596" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A596" s="1">
         <v>595</v>
       </c>
@@ -16333,7 +16331,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="597" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A597" s="1">
         <v>596</v>
       </c>
@@ -16347,7 +16345,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="598" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A598" s="1">
         <v>597</v>
       </c>
@@ -16361,7 +16359,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="599" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A599" s="1">
         <v>598</v>
       </c>
@@ -16375,7 +16373,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="600" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A600" s="1">
         <v>599</v>
       </c>
@@ -16389,10 +16387,10 @@
         <v>926</v>
       </c>
       <c r="F600" s="1" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="601" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="601" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A601" s="1">
         <v>600</v>
       </c>
@@ -16406,7 +16404,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="602" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A602" s="1">
         <v>601</v>
       </c>
@@ -16440,7 +16438,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="604" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A604" s="1">
         <v>603</v>
       </c>
@@ -16461,8 +16459,8 @@
       <c r="B605" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="C605" s="10" t="s">
-        <v>370</v>
+      <c r="C605" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E605" s="1" t="s">
         <v>34</v>
@@ -16483,7 +16481,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="606" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A606" s="1">
         <v>605</v>
       </c>
@@ -16497,7 +16495,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="607" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A607" s="1">
         <v>606</v>
       </c>
@@ -16517,7 +16515,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="608" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A608" s="1">
         <v>607</v>
       </c>
@@ -16531,7 +16529,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="609" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A609" s="1">
         <v>608</v>
       </c>
@@ -16565,7 +16563,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="611" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A611" s="1">
         <v>610</v>
       </c>
@@ -16586,14 +16584,14 @@
       <c r="B612" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="C612" s="10" t="s">
-        <v>370</v>
+      <c r="C612" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E612" s="1" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A613" s="1">
         <v>612</v>
       </c>
@@ -16614,8 +16612,8 @@
       <c r="B614" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="C614" s="10" t="s">
-        <v>370</v>
+      <c r="C614" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E614" s="1" t="s">
         <v>930</v>
@@ -16627,7 +16625,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="615" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A615" s="1">
         <v>614</v>
       </c>
@@ -16641,7 +16639,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="616" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A616" s="1">
         <v>615</v>
       </c>
@@ -16655,7 +16653,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A617" s="1">
         <v>616</v>
       </c>
@@ -16713,7 +16711,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="619" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A619" s="1">
         <v>618</v>
       </c>
@@ -16753,7 +16751,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="621" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A621" s="1">
         <v>620</v>
       </c>
@@ -16782,7 +16780,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="622" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A622" s="1">
         <v>621</v>
       </c>
@@ -16796,7 +16794,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="623" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A623" s="1">
         <v>622</v>
       </c>
@@ -16810,7 +16808,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="624" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A624" s="1">
         <v>623</v>
       </c>
@@ -16824,7 +16822,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" s="1">
         <v>624</v>
       </c>
@@ -16838,7 +16836,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" s="1">
         <v>625</v>
       </c>
@@ -16859,8 +16857,8 @@
       <c r="B627" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="C627" s="10" t="s">
-        <v>370</v>
+      <c r="C627" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="D627" s="1" t="s">
         <v>363</v>
@@ -16869,7 +16867,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="628" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" s="1">
         <v>627</v>
       </c>
@@ -16886,7 +16884,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="629" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" s="1">
         <v>628</v>
       </c>
@@ -16909,7 +16907,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="630" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" s="1">
         <v>629</v>
       </c>
@@ -16926,7 +16924,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" s="1">
         <v>630</v>
       </c>
@@ -16940,7 +16938,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" s="1">
         <v>631</v>
       </c>
@@ -16964,8 +16962,8 @@
       <c r="B633" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C633" s="10" t="s">
-        <v>370</v>
+      <c r="C633" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E633" s="1" t="s">
         <v>34</v>
@@ -16983,7 +16981,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" s="1">
         <v>633</v>
       </c>
@@ -17003,7 +17001,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" s="1">
         <v>634</v>
       </c>
@@ -17040,7 +17038,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" s="1">
         <v>636</v>
       </c>
@@ -17054,7 +17052,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" s="1">
         <v>637</v>
       </c>
@@ -17080,7 +17078,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" s="1">
         <v>638</v>
       </c>
@@ -17100,7 +17098,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" s="1">
         <v>639</v>
       </c>
@@ -17117,7 +17115,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="641" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A641" s="1">
         <v>640</v>
       </c>
@@ -17138,8 +17136,8 @@
       <c r="B642" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="C642" s="10" t="s">
-        <v>370</v>
+      <c r="C642" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D642" s="1" t="s">
         <v>363</v>
@@ -17148,7 +17146,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="643" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A643" s="1">
         <v>642</v>
       </c>
@@ -17172,8 +17170,8 @@
       <c r="B644" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="C644" s="10" t="s">
-        <v>370</v>
+      <c r="C644" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E644" s="1" t="s">
         <v>34</v>
@@ -17188,7 +17186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="645" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A645" s="1">
         <v>644</v>
       </c>
@@ -17208,7 +17206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="646" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A646" s="1">
         <v>645</v>
       </c>
@@ -17222,7 +17220,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="647" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A647" s="1">
         <v>646</v>
       </c>
@@ -17242,7 +17240,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="648" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A648" s="1">
         <v>647</v>
       </c>
@@ -17287,8 +17285,8 @@
       <c r="B649" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="C649" s="10" t="s">
-        <v>370</v>
+      <c r="C649" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E649" s="1" t="s">
         <v>931</v>
@@ -17297,7 +17295,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="650" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A650" s="1">
         <v>649</v>
       </c>
@@ -17314,7 +17312,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="651" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A651" s="1">
         <v>650</v>
       </c>
@@ -17340,7 +17338,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="652" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A652" s="1">
         <v>651</v>
       </c>
@@ -17354,7 +17352,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="653" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A653" s="1">
         <v>652</v>
       </c>
@@ -17368,7 +17366,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="654" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A654" s="1">
         <v>653</v>
       </c>
@@ -17382,7 +17380,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="655" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A655" s="1">
         <v>654</v>
       </c>
@@ -17396,7 +17394,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="656" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A656" s="1">
         <v>655</v>
       </c>
@@ -17413,7 +17411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="657" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A657" s="1">
         <v>656</v>
       </c>
@@ -17427,7 +17425,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="658" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A658" s="1">
         <v>657</v>
       </c>
@@ -17451,8 +17449,8 @@
       <c r="B659" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="C659" s="10" t="s">
-        <v>370</v>
+      <c r="C659" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E659" s="1" t="s">
         <v>926</v>
@@ -17465,8 +17463,8 @@
       <c r="B660" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="C660" s="10" t="s">
-        <v>370</v>
+      <c r="C660" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E660" s="1" t="s">
         <v>926</v>
@@ -17475,7 +17473,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="661" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A661" s="1">
         <v>660</v>
       </c>
@@ -17499,8 +17497,8 @@
       <c r="B662" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="C662" s="10" t="s">
-        <v>370</v>
+      <c r="C662" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E662" s="1" t="s">
         <v>930</v>
@@ -17522,8 +17520,8 @@
       <c r="B663" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="C663" s="10" t="s">
-        <v>370</v>
+      <c r="C663" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E663" s="1" t="s">
         <v>60</v>
@@ -17557,8 +17555,8 @@
       <c r="B664" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="C664" s="10" t="s">
-        <v>370</v>
+      <c r="C664" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="D664" s="1" t="s">
         <v>383</v>
@@ -17576,7 +17574,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="665" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A665" s="1">
         <v>664</v>
       </c>
@@ -17597,8 +17595,8 @@
       <c r="B666" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="C666" s="10" t="s">
-        <v>370</v>
+      <c r="C666" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E666" s="1" t="s">
         <v>901</v>
@@ -17607,7 +17605,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="667" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A667" s="1">
         <v>666</v>
       </c>
@@ -17621,7 +17619,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="668" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A668" s="1">
         <v>667</v>
       </c>
@@ -17650,7 +17648,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="669" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A669" s="1">
         <v>668</v>
       </c>
@@ -17673,7 +17671,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="670" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A670" s="1">
         <v>669</v>
       </c>
@@ -17694,8 +17692,8 @@
       <c r="B671" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="C671" s="10" t="s">
-        <v>370</v>
+      <c r="C671" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E671" s="1" t="s">
         <v>931</v>
@@ -17722,8 +17720,8 @@
       <c r="B673" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C673" s="10" t="s">
-        <v>370</v>
+      <c r="C673" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E673" s="1" t="s">
         <v>34</v>
@@ -17735,7 +17733,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="674" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A674" s="1">
         <v>673</v>
       </c>
@@ -17752,7 +17750,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="675" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A675" s="1">
         <v>674</v>
       </c>
@@ -17769,7 +17767,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="676" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A676" s="1">
         <v>675</v>
       </c>
@@ -17792,7 +17790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="677" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A677" s="1">
         <v>676</v>
       </c>
@@ -17815,7 +17813,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="678" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A678" s="1">
         <v>677</v>
       </c>
@@ -17838,7 +17836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="679" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A679" s="1">
         <v>678</v>
       </c>
@@ -17873,7 +17871,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="680" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A680" s="1">
         <v>679</v>
       </c>
@@ -17887,7 +17885,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="681" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A681" s="1">
         <v>680</v>
       </c>
@@ -17901,7 +17899,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="682" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A682" s="1">
         <v>681</v>
       </c>
@@ -17945,7 +17943,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="683" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A683" s="1">
         <v>682</v>
       </c>
@@ -17982,7 +17980,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="685" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A685" s="1">
         <v>684</v>
       </c>
@@ -17996,7 +17994,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="686" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A686" s="1">
         <v>685</v>
       </c>
@@ -18010,7 +18008,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="687" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A687" s="1">
         <v>686</v>
       </c>
@@ -18034,8 +18032,8 @@
       <c r="B688" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="C688" s="10" t="s">
-        <v>370</v>
+      <c r="C688" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E688" s="1" t="s">
         <v>34</v>
@@ -18050,7 +18048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="689" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A689" s="1">
         <v>688</v>
       </c>
@@ -18070,7 +18068,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="690" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A690" s="1">
         <v>689</v>
       </c>
@@ -18084,7 +18082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A691" s="1">
         <v>690</v>
       </c>
@@ -18101,7 +18099,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="692" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A692" s="1">
         <v>691</v>
       </c>
@@ -18115,7 +18113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A693" s="1">
         <v>692</v>
       </c>
@@ -18129,7 +18127,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="694" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A694" s="1">
         <v>693</v>
       </c>
@@ -18155,7 +18153,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="695" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A695" s="1">
         <v>694</v>
       </c>
@@ -18178,7 +18176,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="696" spans="1:15" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="1">
         <v>695</v>
       </c>
@@ -18192,7 +18190,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="697" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A697" s="1">
         <v>696</v>
       </c>
@@ -18206,7 +18204,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="698" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A698" s="1">
         <v>697</v>
       </c>
@@ -18250,7 +18248,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="699" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A699" s="1">
         <v>698</v>
       </c>
@@ -18264,7 +18262,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="700" spans="1:15" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="1">
         <v>699</v>
       </c>
@@ -18278,7 +18276,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="701" spans="1:15" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="1">
         <v>700</v>
       </c>
@@ -18295,7 +18293,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="702" spans="1:15" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="1">
         <v>701</v>
       </c>
@@ -18316,8 +18314,8 @@
       <c r="B703" s="1" t="s">
         <v>865</v>
       </c>
-      <c r="C703" s="10" t="s">
-        <v>370</v>
+      <c r="C703" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E703" s="1" t="s">
         <v>926</v>
@@ -18326,7 +18324,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="704" spans="1:15" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="1">
         <v>703</v>
       </c>
@@ -18349,7 +18347,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="705" spans="1:16" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="1">
         <v>704</v>
       </c>
@@ -18366,7 +18364,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="706" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A706" s="1">
         <v>705</v>
       </c>
@@ -18380,7 +18378,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="707" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A707" s="1">
         <v>706</v>
       </c>
@@ -18417,7 +18415,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="709" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A709" s="1">
         <v>708</v>
       </c>
@@ -18434,7 +18432,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="710" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A710" s="1">
         <v>709</v>
       </c>
@@ -18451,7 +18449,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="711" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A711" s="1">
         <v>710</v>
       </c>
@@ -18483,7 +18481,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="712" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A712" s="1">
         <v>711</v>
       </c>
@@ -18529,7 +18527,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="714" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A714" s="1">
         <v>713</v>
       </c>
@@ -18552,7 +18550,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="715" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A715" s="1">
         <v>714</v>
       </c>
@@ -18569,7 +18567,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="716" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A716" s="1">
         <v>715</v>
       </c>
@@ -18583,7 +18581,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="717" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A717" s="1">
         <v>716</v>
       </c>
@@ -18630,7 +18628,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="718" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A718" s="1">
         <v>717</v>
       </c>
@@ -18650,7 +18648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="719" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A719" s="1">
         <v>718</v>
       </c>
@@ -18677,8 +18675,8 @@
       <c r="B720" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="C720" s="10" t="s">
-        <v>370</v>
+      <c r="C720" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D720" s="1" t="s">
         <v>363</v>
@@ -18687,7 +18685,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="721" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A721" s="1">
         <v>720</v>
       </c>
@@ -18701,7 +18699,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="722" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A722" s="1">
         <v>721</v>
       </c>
@@ -18721,7 +18719,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="723" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A723" s="1">
         <v>722</v>
       </c>
@@ -18738,7 +18736,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="724" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A724" s="1">
         <v>723</v>
       </c>
@@ -18761,7 +18759,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="725" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A725" s="1">
         <v>724</v>
       </c>
@@ -18778,7 +18776,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="726" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A726" s="1">
         <v>725</v>
       </c>
@@ -18795,7 +18793,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="727" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A727" s="1">
         <v>726</v>
       </c>
@@ -18827,7 +18825,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="728" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A728" s="1">
         <v>727</v>
       </c>
@@ -18841,7 +18839,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="729" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A729" s="1">
         <v>728</v>
       </c>
@@ -18870,7 +18868,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="730" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A730" s="1">
         <v>729</v>
       </c>
@@ -18890,7 +18888,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="731" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A731" s="1">
         <v>730</v>
       </c>
@@ -18920,8 +18918,8 @@
       <c r="B732" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C732" s="10" t="s">
-        <v>370</v>
+      <c r="C732" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E732" s="1" t="s">
         <v>387</v>
@@ -18936,7 +18934,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="733" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A733" s="1">
         <v>732</v>
       </c>
@@ -18950,7 +18948,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="734" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A734" s="1">
         <v>733</v>
       </c>
@@ -18976,7 +18974,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="735" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A735" s="1">
         <v>734</v>
       </c>
@@ -18990,7 +18988,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="736" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A736" s="1">
         <v>735</v>
       </c>
@@ -19014,8 +19012,8 @@
       <c r="B737" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="C737" s="10" t="s">
-        <v>370</v>
+      <c r="C737" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E737" s="1" t="s">
         <v>901</v>
@@ -19028,8 +19026,8 @@
       <c r="B738" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="C738" s="10" t="s">
-        <v>370</v>
+      <c r="C738" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D738" s="1" t="s">
         <v>363</v>
@@ -19038,7 +19036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="739" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A739" s="1">
         <v>738</v>
       </c>
@@ -19072,7 +19070,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="741" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A741" s="1">
         <v>740</v>
       </c>
@@ -19086,7 +19084,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="742" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A742" s="1">
         <v>741</v>
       </c>
@@ -19124,7 +19122,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="743" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A743" s="1">
         <v>742</v>
       </c>
@@ -19154,8 +19152,8 @@
       <c r="B744" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="C744" s="10" t="s">
-        <v>370</v>
+      <c r="C744" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E744" s="1" t="s">
         <v>34</v>
@@ -19173,10 +19171,10 @@
         <v>62</v>
       </c>
       <c r="J744" s="1" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="745" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="745" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A745" s="1">
         <v>744</v>
       </c>
@@ -19196,7 +19194,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="746" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A746" s="1">
         <v>745</v>
       </c>
@@ -19217,8 +19215,8 @@
       <c r="B747" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C747" s="10" t="s">
-        <v>370</v>
+      <c r="C747" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E747" s="1" t="s">
         <v>338</v>
@@ -19246,8 +19244,8 @@
       <c r="B748" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="C748" s="10" t="s">
-        <v>370</v>
+      <c r="C748" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E748" s="1" t="s">
         <v>0</v>
@@ -19269,8 +19267,8 @@
       <c r="B749" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="C749" s="10" t="s">
-        <v>370</v>
+      <c r="C749" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="D749" s="1" t="s">
         <v>383</v>
@@ -19282,7 +19280,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="750" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A750" s="1">
         <v>749</v>
       </c>
@@ -19299,7 +19297,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="751" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A751" s="1">
         <v>750</v>
       </c>
@@ -19316,7 +19314,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="752" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A752" s="1">
         <v>751</v>
       </c>
@@ -19351,8 +19349,8 @@
       <c r="B754" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="C754" s="10" t="s">
-        <v>370</v>
+      <c r="C754" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D754" s="1" t="s">
         <v>756</v>
@@ -19361,7 +19359,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" s="1">
         <v>754</v>
       </c>
@@ -19405,8 +19403,8 @@
       <c r="B757" s="9" t="s">
         <v>1241</v>
       </c>
-      <c r="C757" s="10" t="s">
-        <v>735</v>
+      <c r="C757" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E757" s="1" t="s">
         <v>930</v>
@@ -19431,8 +19429,8 @@
       <c r="B758" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="C758" s="10" t="s">
-        <v>370</v>
+      <c r="C758" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E758" s="1" t="s">
         <v>34</v>
@@ -19467,7 +19465,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" s="1">
         <v>759</v>
       </c>
@@ -19494,14 +19492,11 @@
       <c r="C761" s="10" t="s">
         <v>735</v>
       </c>
-      <c r="D761" s="1" t="s">
-        <v>756</v>
-      </c>
       <c r="E761" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" s="1">
         <v>761</v>
       </c>
@@ -19518,7 +19513,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" s="1">
         <v>762</v>
       </c>
@@ -19545,7 +19540,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="764" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" s="1">
         <v>763</v>
       </c>
@@ -19560,7 +19555,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="765" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765" s="1">
         <v>764</v>
       </c>
@@ -19574,7 +19569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" s="1">
         <v>765</v>
       </c>
@@ -19591,7 +19586,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="767" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A767" s="1">
         <v>766</v>
       </c>
@@ -19605,7 +19600,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="768" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768" s="1">
         <v>767</v>
       </c>
@@ -19625,7 +19620,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="769" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A769" s="1">
         <v>768</v>
       </c>
@@ -19642,7 +19637,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="770" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A770" s="1">
         <v>769</v>
       </c>
@@ -19666,8 +19661,8 @@
       <c r="B771" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="C771" s="10" t="s">
-        <v>370</v>
+      <c r="C771" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E771" s="1" t="s">
         <v>901</v>
@@ -19676,7 +19671,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="772" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A772" s="1">
         <v>771</v>
       </c>
@@ -19696,7 +19691,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="773" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A773" s="1">
         <v>772</v>
       </c>
@@ -19713,7 +19708,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="774" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A774" s="1">
         <v>773</v>
       </c>
@@ -19758,7 +19753,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="777" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A777" s="1">
         <v>776</v>
       </c>
@@ -19772,7 +19767,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="778" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A778" s="1">
         <v>777</v>
       </c>
@@ -19789,7 +19784,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="779" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A779" s="1">
         <v>778</v>
       </c>
@@ -19820,7 +19815,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="781" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A781" s="1">
         <v>780</v>
       </c>
@@ -19848,7 +19843,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="783" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A783" s="1">
         <v>782</v>
       </c>
@@ -19868,7 +19863,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="784" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A784" s="1">
         <v>783</v>
       </c>
@@ -19882,7 +19877,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="785" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A785" s="1">
         <v>784</v>
       </c>
@@ -19896,7 +19891,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="786" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A786" s="1">
         <v>785</v>
       </c>
@@ -19910,7 +19905,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="787" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A787" s="1">
         <v>786</v>
       </c>
@@ -19924,7 +19919,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="788" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A788" s="1">
         <v>787</v>
       </c>
@@ -19938,7 +19933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="789" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A789" s="1">
         <v>788</v>
       </c>
@@ -19952,7 +19947,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="790" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A790" s="1">
         <v>789</v>
       </c>
@@ -19966,7 +19961,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="791" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A791" s="1">
         <v>790</v>
       </c>
@@ -19983,7 +19978,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="792" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A792" s="1">
         <v>791</v>
       </c>
@@ -20004,8 +19999,8 @@
       <c r="B793" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="C793" s="10" t="s">
-        <v>370</v>
+      <c r="C793" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E793" s="1" t="s">
         <v>930</v>
@@ -20017,7 +20012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="794" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" s="1">
         <v>793</v>
       </c>
@@ -20031,7 +20026,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="795" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" s="1">
         <v>794</v>
       </c>
@@ -20045,7 +20040,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="796" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" s="1">
         <v>795</v>
       </c>
@@ -20068,7 +20063,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="797" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" s="1">
         <v>796</v>
       </c>
@@ -20082,7 +20077,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="798" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" s="1">
         <v>797</v>
       </c>
@@ -20096,7 +20091,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="799" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" s="1">
         <v>798</v>
       </c>
@@ -20130,7 +20125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="801" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A801" s="1">
         <v>800</v>
       </c>
@@ -20144,7 +20139,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="802" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A802" s="1">
         <v>801</v>
       </c>
@@ -20158,7 +20153,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="803" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A803" s="1">
         <v>802</v>
       </c>
@@ -20172,7 +20167,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="804" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A804" s="1">
         <v>803</v>
       </c>
@@ -20186,7 +20181,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="805" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A805" s="1">
         <v>804</v>
       </c>
@@ -20200,7 +20195,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="806" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A806" s="1">
         <v>805</v>
       </c>
@@ -20214,7 +20209,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="807" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A807" s="1">
         <v>806</v>
       </c>
@@ -20228,7 +20223,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="808" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A808" s="1">
         <v>807</v>
       </c>
@@ -20262,7 +20257,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="810" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A810" s="1">
         <v>809</v>
       </c>
@@ -20276,7 +20271,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="811" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A811" s="1">
         <v>810</v>
       </c>
@@ -20290,7 +20285,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="812" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A812" s="1">
         <v>811</v>
       </c>
@@ -20304,7 +20299,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="813" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A813" s="1">
         <v>812</v>
       </c>
@@ -20324,7 +20319,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="814" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A814" s="1">
         <v>813</v>
       </c>
@@ -20338,7 +20333,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="815" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A815" s="1">
         <v>814</v>
       </c>
@@ -20352,7 +20347,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="816" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A816" s="1">
         <v>815</v>
       </c>
@@ -20366,7 +20361,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="817" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A817" s="1">
         <v>816</v>
       </c>
@@ -20380,7 +20375,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="818" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A818" s="1">
         <v>817</v>
       </c>
@@ -20401,8 +20396,8 @@
       <c r="B819" s="1" t="s">
         <v>1159</v>
       </c>
-      <c r="C819" s="10" t="s">
-        <v>370</v>
+      <c r="C819" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E819" s="1" t="s">
         <v>926</v>
@@ -20411,7 +20406,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="820" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A820" s="1">
         <v>819</v>
       </c>
@@ -20425,7 +20420,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="821" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A821" s="1">
         <v>820</v>
       </c>
@@ -20439,7 +20434,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="822" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A822" s="1">
         <v>821</v>
       </c>
@@ -20453,7 +20448,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="823" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A823" s="1">
         <v>822</v>
       </c>
@@ -20470,7 +20465,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="824" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A824" s="1">
         <v>823</v>
       </c>
@@ -20484,7 +20479,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="825" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A825" s="1">
         <v>824</v>
       </c>
@@ -20504,7 +20499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="826" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A826" s="1">
         <v>825</v>
       </c>
@@ -20518,7 +20513,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="827" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A827" s="1">
         <v>826</v>
       </c>
@@ -20532,7 +20527,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="828" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A828" s="1">
         <v>827</v>
       </c>
@@ -20552,7 +20547,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="829" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A829" s="1">
         <v>828</v>
       </c>
@@ -20576,8 +20571,8 @@
       <c r="B830" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C830" s="10" t="s">
-        <v>370</v>
+      <c r="C830" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E830" s="1" t="s">
         <v>34</v>
@@ -20589,7 +20584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="831" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A831" s="1">
         <v>830</v>
       </c>
@@ -20606,7 +20601,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="832" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A832" s="1">
         <v>831</v>
       </c>
@@ -20620,7 +20615,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" s="1">
         <v>832</v>
       </c>
@@ -20637,7 +20632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" s="1">
         <v>833</v>
       </c>
@@ -20654,7 +20649,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" s="1">
         <v>834</v>
       </c>
@@ -20678,8 +20673,8 @@
       <c r="B836" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="C836" s="10" t="s">
-        <v>370</v>
+      <c r="C836" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D836" s="1" t="s">
         <v>756</v>
@@ -20688,7 +20683,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" s="1">
         <v>836</v>
       </c>
@@ -20705,7 +20700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" s="1">
         <v>837</v>
       </c>
@@ -20719,7 +20714,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" s="1">
         <v>838</v>
       </c>
@@ -20739,7 +20734,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="840" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" s="1">
         <v>839</v>
       </c>
@@ -20753,7 +20748,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" s="1">
         <v>840</v>
       </c>
@@ -20767,7 +20762,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="842" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" s="1">
         <v>841</v>
       </c>
@@ -20781,7 +20776,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" s="1">
         <v>842</v>
       </c>
@@ -20795,7 +20790,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844" s="1">
         <v>843</v>
       </c>
@@ -20821,7 +20816,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" s="1">
         <v>844</v>
       </c>
@@ -20838,7 +20833,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" s="1">
         <v>845</v>
       </c>
@@ -20855,12 +20850,15 @@
         <v>118</v>
       </c>
     </row>
-    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" s="1">
         <v>846</v>
       </c>
       <c r="B847" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
+      </c>
+      <c r="C847" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D847" s="1" t="s">
         <v>756</v>
@@ -20872,12 +20870,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" s="1">
         <v>847</v>
       </c>
       <c r="B848" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
+      </c>
+      <c r="C848" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D848" s="1" t="s">
         <v>756</v>
@@ -20886,12 +20887,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" s="1">
         <v>848</v>
       </c>
       <c r="B849" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
+      </c>
+      <c r="C849" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D849" s="1" t="s">
         <v>756</v>
@@ -20900,12 +20904,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" s="1">
         <v>849</v>
       </c>
       <c r="B850" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
+      </c>
+      <c r="C850" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D850" s="1" t="s">
         <v>756</v>
@@ -20914,12 +20921,15 @@
         <v>901</v>
       </c>
     </row>
-    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" s="1">
         <v>850</v>
       </c>
       <c r="B851" s="1" t="s">
-        <v>1259</v>
+        <v>1256</v>
+      </c>
+      <c r="C851" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D851" s="1" t="s">
         <v>756</v>
@@ -20928,12 +20938,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="852" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" s="1">
         <v>851</v>
       </c>
       <c r="B852" s="1" t="s">
-        <v>1260</v>
+        <v>1257</v>
+      </c>
+      <c r="C852" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D852" s="1" t="s">
         <v>756</v>
@@ -20942,12 +20955,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" s="1">
         <v>852</v>
       </c>
       <c r="B853" s="1" t="s">
-        <v>1261</v>
+        <v>1258</v>
+      </c>
+      <c r="C853" s="10" t="s">
+        <v>370</v>
       </c>
       <c r="D853" s="1" t="s">
         <v>756</v>
@@ -20959,12 +20975,15 @@
         <v>924</v>
       </c>
     </row>
-    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" s="1">
         <v>853</v>
       </c>
       <c r="B854" s="1" t="s">
-        <v>1262</v>
+        <v>1259</v>
+      </c>
+      <c r="C854" s="10" t="s">
+        <v>370</v>
       </c>
       <c r="D854" s="1" t="s">
         <v>756</v>
@@ -20973,13 +20992,16 @@
         <v>901</v>
       </c>
     </row>
-    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" s="1">
         <v>854</v>
       </c>
       <c r="B855" s="1" t="s">
         <v>608</v>
       </c>
+      <c r="C855" s="1" t="s">
+        <v>359</v>
+      </c>
       <c r="D855" s="1" t="s">
         <v>756</v>
       </c>
@@ -20987,12 +21009,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" s="1">
         <v>855</v>
       </c>
       <c r="B856" s="1" t="s">
-        <v>1263</v>
+        <v>1260</v>
+      </c>
+      <c r="C856" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D856" s="1" t="s">
         <v>756</v>
@@ -21001,12 +21026,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" s="1">
         <v>856</v>
       </c>
       <c r="B857" s="1" t="s">
-        <v>1264</v>
+        <v>1261</v>
+      </c>
+      <c r="C857" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D857" s="1" t="s">
         <v>756</v>
@@ -21015,12 +21043,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" s="1">
         <v>857</v>
       </c>
       <c r="B858" s="1" t="s">
-        <v>1265</v>
+        <v>1262</v>
+      </c>
+      <c r="C858" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D858" s="1" t="s">
         <v>756</v>
@@ -21029,12 +21060,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" s="1">
         <v>858</v>
       </c>
       <c r="B859" s="1" t="s">
-        <v>1266</v>
+        <v>1263</v>
+      </c>
+      <c r="C859" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D859" s="1" t="s">
         <v>756</v>
@@ -21043,12 +21077,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" s="1">
         <v>859</v>
       </c>
       <c r="B860" s="1" t="s">
-        <v>1267</v>
+        <v>1264</v>
+      </c>
+      <c r="C860" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D860" s="1" t="s">
         <v>756</v>
@@ -21057,12 +21094,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" s="1">
         <v>860</v>
       </c>
       <c r="B861" s="1" t="s">
-        <v>1268</v>
+        <v>1265</v>
+      </c>
+      <c r="C861" s="10" t="s">
+        <v>370</v>
       </c>
       <c r="D861" s="1" t="s">
         <v>756</v>
@@ -21074,7 +21114,7 @@
         <v>29</v>
       </c>
       <c r="G861" s="1" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="H861" s="1" t="s">
         <v>73</v>
@@ -21083,12 +21123,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" s="1">
         <v>861</v>
       </c>
       <c r="B862" s="1" t="s">
-        <v>1269</v>
+        <v>1266</v>
+      </c>
+      <c r="C862" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D862" s="1" t="s">
         <v>756</v>
@@ -21097,12 +21140,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" s="1">
         <v>862</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>1270</v>
+        <v>1267</v>
+      </c>
+      <c r="C863" s="10" t="s">
+        <v>370</v>
       </c>
       <c r="D863" s="1" t="s">
         <v>756</v>
@@ -21111,12 +21157,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" s="1">
         <v>863</v>
       </c>
       <c r="B864" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
+      </c>
+      <c r="C864" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D864" s="1" t="s">
         <v>756</v>
@@ -21125,13 +21174,16 @@
         <v>34</v>
       </c>
     </row>
-    <row r="865" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A865" s="1">
         <v>864</v>
       </c>
       <c r="B865" s="1" t="s">
         <v>726</v>
       </c>
+      <c r="C865" s="1" t="s">
+        <v>359</v>
+      </c>
       <c r="D865" s="1" t="s">
         <v>756</v>
       </c>
@@ -21145,12 +21197,15 @@
         <v>899</v>
       </c>
     </row>
-    <row r="866" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A866" s="1">
         <v>865</v>
       </c>
       <c r="B866" s="1" t="s">
-        <v>1272</v>
+        <v>1269</v>
+      </c>
+      <c r="C866" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D866" s="1" t="s">
         <v>756</v>
@@ -21159,12 +21214,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="867" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A867" s="1">
         <v>866</v>
       </c>
       <c r="B867" s="1" t="s">
-        <v>1273</v>
+        <v>1270</v>
+      </c>
+      <c r="C867" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D867" s="1" t="s">
         <v>756</v>
@@ -21173,12 +21231,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="868" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A868" s="1">
         <v>867</v>
       </c>
       <c r="B868" s="1" t="s">
-        <v>1274</v>
+        <v>1271</v>
+      </c>
+      <c r="C868" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D868" s="1" t="s">
         <v>756</v>
@@ -21190,12 +21251,15 @@
         <v>71</v>
       </c>
     </row>
-    <row r="869" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A869" s="1">
         <v>868</v>
       </c>
       <c r="B869" s="1" t="s">
-        <v>1275</v>
+        <v>1272</v>
+      </c>
+      <c r="C869" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D869" s="1" t="s">
         <v>756</v>
@@ -21204,12 +21268,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="870" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A870" s="1">
         <v>869</v>
       </c>
       <c r="B870" s="1" t="s">
-        <v>1276</v>
+        <v>1273</v>
+      </c>
+      <c r="C870" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D870" s="1" t="s">
         <v>756</v>
@@ -21218,12 +21285,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="871" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A871" s="1">
         <v>870</v>
       </c>
       <c r="B871" s="1" t="s">
-        <v>1277</v>
+        <v>1274</v>
+      </c>
+      <c r="C871" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D871" s="1" t="s">
         <v>756</v>
@@ -21232,12 +21302,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="872" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A872" s="1">
         <v>871</v>
       </c>
       <c r="B872" s="1" t="s">
-        <v>1278</v>
+        <v>1275</v>
+      </c>
+      <c r="C872" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D872" s="1" t="s">
         <v>756</v>
@@ -21246,12 +21319,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="873" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A873" s="1">
         <v>872</v>
       </c>
       <c r="B873" s="1" t="s">
-        <v>1279</v>
+        <v>1276</v>
+      </c>
+      <c r="C873" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D873" s="1" t="s">
         <v>756</v>
@@ -21260,12 +21336,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="874" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A874" s="1">
         <v>873</v>
       </c>
       <c r="B874" s="1" t="s">
-        <v>1280</v>
+        <v>1277</v>
+      </c>
+      <c r="C874" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D874" s="1" t="s">
         <v>756</v>
@@ -21274,12 +21353,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="875" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A875" s="1">
         <v>874</v>
       </c>
       <c r="B875" s="1" t="s">
-        <v>1281</v>
+        <v>1278</v>
+      </c>
+      <c r="C875" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D875" s="1" t="s">
         <v>756</v>
@@ -21288,48 +21370,60 @@
         <v>191</v>
       </c>
     </row>
-    <row r="876" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A876" s="1">
         <v>875</v>
       </c>
       <c r="B876" s="1" t="s">
-        <v>1288</v>
+        <v>1285</v>
+      </c>
+      <c r="C876" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E876" s="1" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="877" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A877" s="1">
         <v>876</v>
       </c>
       <c r="B877" s="1" t="s">
-        <v>1290</v>
+        <v>1287</v>
+      </c>
+      <c r="C877" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E877" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="878" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A878" s="1">
         <v>877</v>
       </c>
       <c r="B878" s="1" t="s">
-        <v>1303</v>
+        <v>1300</v>
+      </c>
+      <c r="C878" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="D878" s="1" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="E878" s="1" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="879" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A879" s="1">
         <v>878</v>
       </c>
       <c r="B879" s="1" t="s">
-        <v>1306</v>
+        <v>1303</v>
+      </c>
+      <c r="C879" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E879" s="1" t="s">
         <v>931</v>
@@ -21338,23 +21432,29 @@
         <v>900</v>
       </c>
     </row>
-    <row r="880" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A880" s="1">
         <v>879</v>
       </c>
       <c r="B880" s="1" t="s">
-        <v>1307</v>
+        <v>1304</v>
+      </c>
+      <c r="C880" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="E880" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="881" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A881" s="1">
         <v>880</v>
       </c>
       <c r="B881" s="1" t="s">
-        <v>1308</v>
+        <v>1305</v>
+      </c>
+      <c r="C881" s="10" t="s">
+        <v>370</v>
       </c>
       <c r="E881" s="1" t="s">
         <v>67</v>
@@ -21366,7 +21466,7 @@
         <v>64</v>
       </c>
       <c r="H881" s="1" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="I881" s="1" t="s">
         <v>49</v>
@@ -21390,36 +21490,36 @@
         <v>883</v>
       </c>
       <c r="P881" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="Q881" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="R881" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="S881" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="T881" s="1" t="s">
         <v>1310</v>
       </c>
-      <c r="Q881" s="1" t="s">
-        <v>1284</v>
-      </c>
-      <c r="R881" s="1" t="s">
+      <c r="U881" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="S881" s="1" t="s">
+      <c r="V881" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="T881" s="1" t="s">
+      <c r="W881" s="1" t="s">
         <v>1313</v>
       </c>
-      <c r="U881" s="1" t="s">
-        <v>1314</v>
-      </c>
-      <c r="V881" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="W881" s="1" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="882" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="882" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A882" s="1">
         <v>881</v>
       </c>
       <c r="B882" s="1" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="E882" s="1">
         <v>1</v>
@@ -21446,28 +21546,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="883" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A883" s="1">
         <v>882</v>
       </c>
     </row>
-    <row r="884" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A884" s="1">
         <v>883</v>
       </c>
     </row>
-    <row r="885" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A885" s="1">
         <v>884</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S885" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Download"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="4" showButton="0"/>
     <filterColumn colId="5" showButton="0"/>
     <filterColumn colId="6" showButton="0"/>
@@ -21497,107 +21592,90 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D7D0B87-497F-432C-A5D7-5B64A1E8E7D5}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>1247</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>1248</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B3" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>1291</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>370</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>1292</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" t="s">
+      <c r="B9" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>359</v>
+      </c>
+      <c r="B10" t="s">
         <v>1293</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>370</v>
-      </c>
-      <c r="C18" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="13" t="s">
         <v>1298</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>359</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="14" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="13" t="s">
         <v>1299</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C23" s="14" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C24" s="14" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C25" s="14" t="s">
-        <v>1302</v>
       </c>
     </row>
   </sheetData>
